--- a/06_TPCvIKT/output/pal_food_summary.xlsx
+++ b/06_TPCvIKT/output/pal_food_summary.xlsx
@@ -415,10 +415,18 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="E2"/>
+      <c r="B2" t="n">
+        <v>15.4712589317901</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.144550288267957</v>
+      </c>
+      <c r="D2" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="E2" t="n">
+        <v>16.5</v>
+      </c>
       <c r="F2" t="n">
         <v>0.197373142898155</v>
       </c>
@@ -427,10 +435,18 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3"/>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="E3"/>
+      <c r="B3" t="n">
+        <v>12.8171666664547</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.135611248237949</v>
+      </c>
+      <c r="D3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" t="n">
+        <v>14</v>
+      </c>
       <c r="F3" t="n">
         <v>0.12206686110368</v>
       </c>
@@ -439,10 +455,18 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4"/>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4"/>
+      <c r="B4" t="n">
+        <v>20.8085476200013</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.176628600611206</v>
+      </c>
+      <c r="D4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" t="n">
+        <v>24</v>
+      </c>
       <c r="F4" t="n">
         <v>0.130857125043589</v>
       </c>
@@ -451,10 +475,18 @@
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5"/>
-      <c r="C5"/>
-      <c r="D5"/>
-      <c r="E5"/>
+      <c r="B5" t="n">
+        <v>16.195492204131</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.135491155603766</v>
+      </c>
+      <c r="D5" t="n">
+        <v>14.9999997764826</v>
+      </c>
+      <c r="E5" t="n">
+        <v>17.9999997317791</v>
+      </c>
       <c r="F5" t="n">
         <v>0.0814504044246383</v>
       </c>
@@ -463,10 +495,18 @@
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6"/>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="E6"/>
+      <c r="B6" t="n">
+        <v>10.457066672643</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0862200082753724</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11</v>
+      </c>
       <c r="F6" t="n">
         <v>0.159649317404288</v>
       </c>
@@ -475,10 +515,18 @@
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7"/>
-      <c r="C7"/>
-      <c r="D7"/>
-      <c r="E7"/>
+      <c r="B7" t="n">
+        <v>76.2024924700901</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.599229998929976</v>
+      </c>
+      <c r="D7" t="n">
+        <v>51.2571429253841</v>
+      </c>
+      <c r="E7" t="n">
+        <v>76.8</v>
+      </c>
       <c r="F7" t="n">
         <v>0.17190493900463</v>
       </c>
@@ -487,10 +535,18 @@
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8"/>
-      <c r="C8"/>
-      <c r="D8"/>
-      <c r="E8"/>
+      <c r="B8" t="n">
+        <v>18.833494073853</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.262764937826509</v>
+      </c>
+      <c r="D8" t="n">
+        <v>14.9687500104774</v>
+      </c>
+      <c r="E8" t="n">
+        <v>23.0147055909682</v>
+      </c>
       <c r="F8" t="n">
         <v>0.0818618250255371</v>
       </c>
@@ -499,10 +555,18 @@
       <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9"/>
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="E9"/>
+      <c r="B9" t="n">
+        <v>10.4190833472723</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.288464234412441</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8.94444456218202</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
       <c r="F9" t="n">
         <v>0.0192117108789756</v>
       </c>
@@ -511,10 +575,18 @@
       <c r="A10" t="s">
         <v>14</v>
       </c>
-      <c r="B10"/>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="E10"/>
+      <c r="B10" t="n">
+        <v>14.71429203789</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.341420156919533</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="E10" t="n">
+        <v>17.9999993794105</v>
+      </c>
       <c r="F10" t="n">
         <v>0.0221569024052337</v>
       </c>
@@ -523,10 +595,18 @@
       <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="B11"/>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11"/>
+      <c r="B11" t="n">
+        <v>9.32576281414759</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.758457975297332</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7.1398230237869</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.5652172177861</v>
+      </c>
       <c r="F11" t="n">
         <v>0.0134677718112729</v>
       </c>
@@ -535,10 +615,18 @@
       <c r="A12" t="s">
         <v>16</v>
       </c>
-      <c r="B12"/>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
+      <c r="B12" t="n">
+        <v>205.123404255022</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.243641619795109</v>
+      </c>
+      <c r="D12" t="n">
+        <v>171.105556669279</v>
+      </c>
+      <c r="E12" t="n">
+        <v>223.695947104178</v>
+      </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
